--- a/cronograma_Efata_Eventos_30_12_2025.xlsx
+++ b/cronograma_Efata_Eventos_30_12_2025.xlsx
@@ -42,14 +42,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
-        <bgColor rgb="00D3D3D3"/>
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -496,640 +496,128 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05/01/2026 09:00</t>
+          <t>02/01/2026 08:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>90181/2025</t>
+          <t>005/2025</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
+          <t>Concorrência - Eletrônica</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>COMANDO DA AERONAUTICA</t>
+          <t>MUNICIPIO DE MOJUI DOS CAMPOS</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE MATERIAL DE CONSUMO MECÂNICO PARA GRUPOS GERADORES QUE ESTÃO SOB RESPONSABILIDADE DO CINDACTA IV.</t>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA CONSTRUÇÃO DE PONTE EM CONCRETO ARMADO E PRÉ-MOLDADO, COM 15,00M DE EXTENSÃO POR 5,00M DE LARGURA, LOCALIZADA NA COMUNIDADE DO IGARAPÉ DO MANOEL, ZONA RURAL DO MUNICÍPIO DE MOJUÍ DOS CAMPOS – PA, COM RECURSOS ORIUNDOS DA DEFESA CIVIL NACIONAL, VINCULADA AO MINISTÉRIO DA INTEGRAÇÃO E DO DESENVOLVIMENTO REGIONAL.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>120195</t>
+          <t>5552</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05/01/2026 10:00</t>
+          <t>07/01/2026 08:59</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>024/2025</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>9/2025-00048/2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ARRAIAL DO CABO</t>
+          <t>MUNICIPIO DE PARAGOMINAS</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[LICITANET] - PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS DE ARBITRAGEM DESPORTIVA, A SEREM REALIZADOS EM DIVERSOS EVENTOS EMODALIDADES ESPORTIVAS PROMOVIDOS PELO MUNICÍPIO DE ARRAIAL DO CABO.</t>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - “AQUISIÇÃO DE TUBOS DE CONCRETO ARMADO DESTINADOS A ATENDER ÀS DEMANDAS DA SECRETARIA MUNICIPAL DE INFRAESTRUTURA – SEMINFRA, VISANDO À EXECUÇÃO, MANUTENÇÃO E AMPLIAÇÃO DE OBRAS DE INFRAESTRUTURA URBANA, ESPECIALMENTE EM REDES DE DRENAGEM PLUVIAL E ESGOTAMENTO SANITÁRIO, NO MUNICÍPIO DE PARAGOMINAS/PA”</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05/01/2026 10:00</t>
+          <t>07/01/2026 10:30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>90172/2025</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+          <t>92025039/2025</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE NOVA FRIBURGO</t>
+          <t>MUNICIPIO DE CAPITAO POCO</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA OS SERVIÇOS DE LOCAÇÃO DE PALCOS, PLATAFORMAS TELESCÓPICAS, CABINES E ESTRUTURAS PARA DIVULGAÇÃO PARA EVENTOS, PARA ATENDER AS NECESSIDADES DA SECRETARIA DE TURISMO, DA SECRETARIA DE CULTURA E SECRETARIA DE ESPORTES E LAZER, PELO PERÍODO DE 01 (UM) ANO. </t>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - CONTRATAÇÃO DE EMPRESA PARA FUTURA E EVENTUAL AQUISIÇÃO DE ARTEFATOS DE  CIMENTO, TAIS COMO BLOQUETES,MEIO FIO E TUBOS DE CONCRETO, VISANDO ATENDER ÀS  NECESSIDADES DO MUNICÍPIO DE CAPITÃO POÇO/PA</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>985867</t>
+          <t>1856</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>06/01/2026 09:00</t>
+          <t>12/01/2026 14:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>90148/2025</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+          <t>90024/2025</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>MINISTERIO DA DEFESA</t>
+          <t>MUNICIPIO DE SAO MIGUEL DO GUAMA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO DE BUFFET E COFFEE-BREAK PARA ATENDER OS EVENTOS INSTITUCIONAIS DA ESCOLA SUPERIOR DE GUERRA     </t>
+          <t>REGISTRO DE PREÇOS PARA AQUISIÇÃO DE TUBOS DE CONCRETO ARMADO, BLOCOS VAZADOS, PISOS INTERTRAVADOS E PISOS TÁTEIS, DESTINADOS A ATENDER AS DEMANDAS DE DRENAGEM PLUVIAL E  INFRAESTRUTURA URBANA E RURAL DO MUNICÍPIO DE SÃO MIGUEL DO GUAMÁ/PA.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110402</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>06/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>90831/2025</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE RIO DE JANEIRO</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>CONTRATAÇÃO DE EMPRESAS ESPECIALIZADAS NA PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE BUFFET – COFFEE BREAK I, COFFEE BREAK II E BRUNCH, PERTENCENTES À CLASSE 2201,  A SEREM DISPONIBILIZADOS EM EVENTOS E AÇÕES DA SECRETARIA ESPECIAL DE CIDADANIA E FAMÍLIA NA CIDADE DO RIO DE JANEIRO, POSSIBILITANDO GARANTIR O PERFEITO FUNCIONAMENTO DAS DEMANDAS OPERACIONAIS DESTA ADMINISTRAÇÃO PÚBLICA, NAS CONDIÇÕES, QUANTIDADES E EXIGÊNCIAS ESTABELECIDAS NO TERMO DE REFERÊNCIA, DEVENDO ESTAR I</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>986001</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>06/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>90023/2025</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>COMANDO DA MARINHA</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>CONTRATAÇÃO DE EMPRESA PRESTADORA DE SERVIÇOS DE LOCAÇÃO DE ITENS DIVERSOS DESTINADOS A EVENTOS INSTITUCIONAIS.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>731060</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>06/01/2026 11:00</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>90038/2025</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DO RIO DE JANEIRO</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PREÇOS PARA A PRESTAÇÃO DE SERVIÇOS DE TRADUÇÃO-INTERPRETAÇÃO DA LÍNGUA BRASILEIRA DE SINAIS (LIBRAS) PARA A LÍNGUA PORTUGUESA E VICE-VERSA, NAS MODALIDADES FALADA, SINALIZADA OU ESCRITA, NAS FORMAS SIMULTÂNEA OU CONSECUTIVA, AO VIVO OU ENSAIADA, GRAVADA OU NÃO, DE AULAS E EVENTOS PROMOVIDOS OU APOIADOS PELO TRIBUNAL DE CONTAS DO ESTADO DO RIO DE JANEIRO E DE SUA ESCOLA DE GESTÃO (ECG/TCE-RJ), DENTRO DO MUNICÍPIO DO RIO DE JANEIRO.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>925464</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>07/01/2026 08:00</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>39/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Dispensa</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>COMANDO DO EXERCITO</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA O FORNECIMENTO DE MATERIAIS DE FESTIVIDADE E HOMENAGEM, SENDO ESTES: CANECAS PERSONALIZADAS, MOEDAS COMEMORATIVAS E BLOCOS DE ANOTAÇÕES, TODOS PRODUZIDOS COM A ARTE OFICIAL FORNECIDA PELA PREFEITURA MILITAR DA ZONA SUL, DESTINADOS ÀS AÇÕES INSTITUCIONAIS, EVENTOS COMEMORATIVOS E CERIMÔNIAS OFICIAIS DO ÓRGÃO.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>160283</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>07/01/2026 09:30</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>001/2026/2025</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Dispensa</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ITATIAIA</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE EQUIPAMENTOS E MATERIAIS PERMANENTES PARA AULAS, ENTREVISTAS, SINE ITINERANTE E DEMAIS EVENTOS DA SECRETARIA.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>000000001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>07/01/2026 13:00</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>90128/2025</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>TRIBUNAL REGIONAL FEDERAL DA 2 REGIAO</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA FORNECIMENTO DE GÊNEROS ALIMENTÍCIOS, DE FORMA PARCELADA, MEDIANTE REQUISIÇÃO, PARA CONFECÇÃO DE LANCHES A SEREM SERVIDOS NAS SESSÕES DE JULGAMENTO, SESSÕES PLENÁRIAS, CURSOS, PALESTRAS E OUTROS EVENTOS NO TRIBUNAL REGIONAL FEDERAL DA 2ª REGIÃO</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>090028</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>08/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>90153/2025</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE NOVA FRIBURGO</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGISTO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA  ESPECIALIZADA PARA OS SERVIÇOS DE: LOCAÇÃO DE TELÃO DE LED,  TRANSMISSÃO SIMULTÂNEA PARA TELÃO E VIDEO JOCKER - VJ PARA  EVENTOS, PARA ATENDER AS NECESSIDADES DA SECRETARIA DE CULTURA, SECRETARIA  DE TURISMO E DA SECRETARIA DE ESPORTE E LAZER, PELO PERÍODO DE 01 (UM) ANO.  </t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>985867</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>08/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>003/2025</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>FUNDACAO MUNICIPAL DE ESPORTES</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>[LICITANET] - PRESTAÇÃO DE SERVIÇOS DE ENGENHARIA PARA LOCAÇÃO, MONTAGEM E DESMONTAGEM DE ARENA ESPORTIVA E TODA ESTRUTURA NECESSÁRIA, PARA ATENDER OS EVENTOS ESPORTIVOS QUE SERÃO REALIZADOS PELA FUNDAÇÃO MUNICIPAL DE ESPORTES – FME, NOS MESES DE JANEIRO E FEVEREIRO, DURANTE O VERÃO DE 2026 NA PRAIA FAROL DE SÃO THOMÉ</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1638</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>08/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>90034/2025</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE MARICA</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PREÇOS PARA A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ATENDIMENTO MÉDICO E REMOÇÃO EM EVENTOS APOIADOS E/OU REALIZADOS NO MUNICÍPIO DE MARICÁ, A FIM DE ATENDER AS NECESSIDADES DA SECRETARIA DE TURISMO, COMÉRCIO, INDÚSTRIA E MERCADO INTERNO, DEVIDAMENTE DESCRITOS, CARACTERIZADOS E ESPECIFICADOS NESTE EDITAL E/OU NO TERMO DE REFERÊNCIA, NA FORMA DA LEI.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>985853</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>09/01/2026 08:00</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>90127/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>COMANDO DO EXERCITO</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE DECORAÇÃO DE EVENTOS E SOLENIDADES OFICIAIS DA ACADEMIA MILITAR DAS AGULHAS NEGRAS (AMAN),</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>160249</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>90005/2025</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>MINISTERIO DA CIENCIA, TECNOLOGIA E INOVACOES</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA DOS GRUPOS GERADORES E RESPECTIVOS SISTEMAS DE CONTROLE, TRANSFERÊNCIA E ABASTECIMENTO DE COMBUSTÍVEL, INSTALADOS NO CENTRO BRASILEIRO DE PESQUISAS FÍSICAS – CBPF.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>240120</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/01/2026 11:00</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>90016/2025</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE NITEROI</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PREÇOS PARA PRESTAÇÃO DO SERVIÇO DE BUFFET, CONFORME CONDIÇÕES, QUANTIDADES E EXIGÊNCIAS ESTABELECIDAS NO EDITAL E SEUS ANEXOS.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>985865</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>13/01/2026 09:00</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>90061/2025</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE SAO PEDRO DA ALDEIA</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PREÇOS PARA SELEÇÃO DA PROPOSTA MAIS VANTAJOSA PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA QUALIFICADA PARA PRESTAÇÃO DE SERVIÇOS DE LOCAÇÃO DE INFRAESTRUTURA TEMPORÁRIA PARA EVENTOS, DE ACORDO COM AS CONDIÇÕES E DEMAIS ESPECIFICAÇÕES CONTIDAS NO EDITAL E SEUS ANEXOS.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>985903</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>14/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>90176/2025</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE NOVA FRIBURGO</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA OS SERVIÇOS DE LOCAÇÃO DE MÓDULOS OCTANORM, TENDAS, GRADIS, ARQUIBANCADAS E PISOS PARA EVENTOS, PARA ATENDER AS NECESSIDADES DA SECRETARIA DE TURISMO E DA SECRETARIA DE CULTURA, PELO PERÍODO DE 01 (UM) ANO</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>985867</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>14/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>001/2026/2025</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ITATIAIA</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CRONOMETRAGEM E ORGANIZAÇÃO DE EVENTOS ESPORTIVOS (CORRIDA/CAMINHADA, MOUNTAIN BIKE, BIKE SPEED E DOWNHILL), DESTINADOS À SECRETARIA MUNICIPAL DE ESPORTE E LAZER DO MUNICÍPIO DE ITATIAIA/RJ, PELO SISTEMA DE REGISTRO DE PREÇOS, POR UM PERÍODO DE 12 (DOZE) MESES, PRORROGÁVEL POR IGUAL PERÍODO.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>000000001</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>14/01/2026 10:00</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>031/2025</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ITAOCARA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[LICITANET] - REGISTRO DE PREÇOS PARA EVENTUAIS E FUTURAS PRESTAÇÕES DE SERVIÇOS CONCERNENTES APOIO OPERACIONAL, VISANDO ATENDER AOS EVENTOS E FESTAS REALIZADAS PELA SECRETARIA MUNICIPAL DE TURISMO E CULTURA DA PREFEITURA DO MUNICÍPIO DE ITAOCARA/RJ. </t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1508</t>
+          <t>980551</t>
         </is>
       </c>
     </row>
